--- a/CONFIGURACION_VEHICULAR_LIMPIO.xlsx
+++ b/CONFIGURACION_VEHICULAR_LIMPIO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imetricasas-my.sharepoint.com/personal/juanmatiz_imetrica_co/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f8a3802af127234b/Documentos/GitHub/sicetac-api/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{4585CAA3-6B70-4003-B374-4AB874E847AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22180" windowHeight="14140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -195,15 +195,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -511,15 +508,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="63.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29.7109375" customWidth="1"/>
+    <col min="1" max="1" width="63.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
@@ -535,11 +532,11 @@
       <c r="E1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -559,7 +556,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -579,7 +576,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -599,7 +596,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -619,7 +616,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -639,7 +636,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -659,7 +656,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -679,7 +676,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -699,7 +696,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -719,7 +716,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>21</v>
       </c>
